--- a/machines_cleaned.xlsx
+++ b/machines_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2183A7A1-95B3-4E50-98B8-FA2861C6D282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0F773E-05C1-422A-AEA5-F9454FF87C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,11 +1152,12 @@
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>

--- a/machines_cleaned.xlsx
+++ b/machines_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFEE78F-7E1B-44B4-89CD-F27041DB33EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B201E78-5F79-43D8-8ADE-5974849FDF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$118</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="253">
   <si>
     <t>OEM</t>
   </si>
@@ -67,6 +67,594 @@
     <t>Daylight Min (mm)</t>
   </si>
   <si>
+    <t>ENGEL</t>
+  </si>
+  <si>
+    <t>Duo</t>
+  </si>
+  <si>
+    <t>ES 7050/1100</t>
+  </si>
+  <si>
+    <t>Large dual platen machine</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>e-victory 170/100</t>
+  </si>
+  <si>
+    <t>Tie-barless design</t>
+  </si>
+  <si>
+    <t>ES Series</t>
+  </si>
+  <si>
+    <t>ES 2050/500</t>
+  </si>
+  <si>
+    <t>Hydraulic toggle</t>
+  </si>
+  <si>
+    <t>ES 200/60</t>
+  </si>
+  <si>
+    <t>Older hydraulic machine</t>
+  </si>
+  <si>
+    <t>e-motion</t>
+  </si>
+  <si>
+    <t>e-motion 2440/380</t>
+  </si>
+  <si>
+    <t>All-electric machine</t>
+  </si>
+  <si>
+    <t>ARBURG</t>
+  </si>
+  <si>
+    <t>ALLROUNDER S</t>
+  </si>
+  <si>
+    <t>220 S 250-60</t>
+  </si>
+  <si>
+    <t>Small hydraulic</t>
+  </si>
+  <si>
+    <t>270 S 300-100</t>
+  </si>
+  <si>
+    <t>Compact machine</t>
+  </si>
+  <si>
+    <t>320 S 500-60</t>
+  </si>
+  <si>
+    <t>Small standard</t>
+  </si>
+  <si>
+    <t>320 S 500-150</t>
+  </si>
+  <si>
+    <t>Flexible unit</t>
+  </si>
+  <si>
+    <t>370 S 700-290</t>
+  </si>
+  <si>
+    <t>Mid-size</t>
+  </si>
+  <si>
+    <t>370 S 800-150</t>
+  </si>
+  <si>
+    <t>Standard mid-size</t>
+  </si>
+  <si>
+    <t>420 S 1000-350</t>
+  </si>
+  <si>
+    <t>Mid-large</t>
+  </si>
+  <si>
+    <t>470 S 1300-400</t>
+  </si>
+  <si>
+    <t>Larger mid range</t>
+  </si>
+  <si>
+    <t>520 S 1600-800</t>
+  </si>
+  <si>
+    <t>Large hydraulic</t>
+  </si>
+  <si>
+    <t>570 S 2000-800</t>
+  </si>
+  <si>
+    <t>Large machine</t>
+  </si>
+  <si>
+    <t>630 S 2500-1300</t>
+  </si>
+  <si>
+    <t>High tonnage</t>
+  </si>
+  <si>
+    <t>720 S 3200-2100</t>
+  </si>
+  <si>
+    <t>Heavy duty</t>
+  </si>
+  <si>
+    <t>ALLROUNDER A</t>
+  </si>
+  <si>
+    <t>270 A 300-100</t>
+  </si>
+  <si>
+    <t>Electric compact</t>
+  </si>
+  <si>
+    <t>320 A 500-150</t>
+  </si>
+  <si>
+    <t>Entry electric</t>
+  </si>
+  <si>
+    <t>370 A 700-290</t>
+  </si>
+  <si>
+    <t>Precision mid-size</t>
+  </si>
+  <si>
+    <t>370 A 800-150</t>
+  </si>
+  <si>
+    <t>Common electric</t>
+  </si>
+  <si>
+    <t>420 A 1000-350</t>
+  </si>
+  <si>
+    <t>Precise molding</t>
+  </si>
+  <si>
+    <t>470 A 1300-400</t>
+  </si>
+  <si>
+    <t>High accuracy</t>
+  </si>
+  <si>
+    <t>520 A 1600-800</t>
+  </si>
+  <si>
+    <t>Large precision</t>
+  </si>
+  <si>
+    <t>570 A 2000-800</t>
+  </si>
+  <si>
+    <t>Large electric</t>
+  </si>
+  <si>
+    <t>630 A 2500-1300</t>
+  </si>
+  <si>
+    <t>Heavy electric</t>
+  </si>
+  <si>
+    <t>ALLROUNDER H</t>
+  </si>
+  <si>
+    <t>370 H 700-290</t>
+  </si>
+  <si>
+    <t>Hybrid mid-size</t>
+  </si>
+  <si>
+    <t>420 H 1000-350</t>
+  </si>
+  <si>
+    <t>Hybrid efficiency</t>
+  </si>
+  <si>
+    <t>470 H 1300-400</t>
+  </si>
+  <si>
+    <t>Common hybrid</t>
+  </si>
+  <si>
+    <t>520 H 1600-800</t>
+  </si>
+  <si>
+    <t>Large hybrid</t>
+  </si>
+  <si>
+    <t>570 H 2000-800</t>
+  </si>
+  <si>
+    <t>High productivity</t>
+  </si>
+  <si>
+    <t>630 H 2500-1300</t>
+  </si>
+  <si>
+    <t>Heavy hybrid</t>
+  </si>
+  <si>
+    <t>720 H 3200-2100</t>
+  </si>
+  <si>
+    <t>Large scale production</t>
+  </si>
+  <si>
+    <t>ALLROUNDER C</t>
+  </si>
+  <si>
+    <t>170 C 200-30</t>
+  </si>
+  <si>
+    <t>Very small compact</t>
+  </si>
+  <si>
+    <t>220 C 250-60</t>
+  </si>
+  <si>
+    <t>Compact design</t>
+  </si>
+  <si>
+    <t>270 C 300-100</t>
+  </si>
+  <si>
+    <t>Compact production</t>
+  </si>
+  <si>
+    <t>SUMITOMO</t>
+  </si>
+  <si>
+    <t>SE-EV-A</t>
+  </si>
+  <si>
+    <t>SE50EV-A</t>
+  </si>
+  <si>
+    <t>Small electric precision</t>
+  </si>
+  <si>
+    <t>SE75EV-A</t>
+  </si>
+  <si>
+    <t>Small-mid electric</t>
+  </si>
+  <si>
+    <t>SE130EV-A</t>
+  </si>
+  <si>
+    <t>Mid-size electric</t>
+  </si>
+  <si>
+    <t>SE180EV-A</t>
+  </si>
+  <si>
+    <t>Precision molding</t>
+  </si>
+  <si>
+    <t>SE280EV-A</t>
+  </si>
+  <si>
+    <t>SE350EV-A</t>
+  </si>
+  <si>
+    <t>Large electric high force</t>
+  </si>
+  <si>
+    <t>SE450EV-A</t>
+  </si>
+  <si>
+    <t>High tonnage electric</t>
+  </si>
+  <si>
+    <t>SE500EV-A</t>
+  </si>
+  <si>
+    <t>SE-HDZ</t>
+  </si>
+  <si>
+    <t>SE130HDZ</t>
+  </si>
+  <si>
+    <t>Electric high-speed</t>
+  </si>
+  <si>
+    <t>SE180HDZ</t>
+  </si>
+  <si>
+    <t>Thin-wall applications</t>
+  </si>
+  <si>
+    <t>SE220HDZ</t>
+  </si>
+  <si>
+    <t>High-speed packaging</t>
+  </si>
+  <si>
+    <t>SE280HDZ</t>
+  </si>
+  <si>
+    <t>Fast cycle</t>
+  </si>
+  <si>
+    <t>SE350HDZ</t>
+  </si>
+  <si>
+    <t>High-speed large</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>SD30</t>
+  </si>
+  <si>
+    <t>Small electric</t>
+  </si>
+  <si>
+    <t>SD55</t>
+  </si>
+  <si>
+    <t>Compact precision</t>
+  </si>
+  <si>
+    <t>SD75</t>
+  </si>
+  <si>
+    <t>Standard electric</t>
+  </si>
+  <si>
+    <t>SD130</t>
+  </si>
+  <si>
+    <t>SD180</t>
+  </si>
+  <si>
+    <t>High precision</t>
+  </si>
+  <si>
+    <t>SD280</t>
+  </si>
+  <si>
+    <t>SD350</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>El-Exis SP</t>
+  </si>
+  <si>
+    <t>SP200</t>
+  </si>
+  <si>
+    <t>Ultra-high speed</t>
+  </si>
+  <si>
+    <t>SP350</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>SP450</t>
+  </si>
+  <si>
+    <t>Thin-wall</t>
+  </si>
+  <si>
+    <t>SP500</t>
+  </si>
+  <si>
+    <t>Large packaging</t>
+  </si>
+  <si>
+    <t>Systec</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>Hydraulic</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Standard hydraulic</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Heavy hydraulic</t>
+  </si>
+  <si>
+    <t>HAITIAN</t>
+  </si>
+  <si>
+    <t>MA Series</t>
+  </si>
+  <si>
+    <t>MA1200</t>
+  </si>
+  <si>
+    <t>Mars standard</t>
+  </si>
+  <si>
+    <t>MA1600</t>
+  </si>
+  <si>
+    <t>Mars mid-size</t>
+  </si>
+  <si>
+    <t>MA2000</t>
+  </si>
+  <si>
+    <t>Mars mid-high</t>
+  </si>
+  <si>
+    <t>MA2500</t>
+  </si>
+  <si>
+    <t>Mars large</t>
+  </si>
+  <si>
+    <t>MA3200</t>
+  </si>
+  <si>
+    <t>Mars larger</t>
+  </si>
+  <si>
+    <t>MA3800</t>
+  </si>
+  <si>
+    <t>MA4700</t>
+  </si>
+  <si>
+    <t>Mars heavy</t>
+  </si>
+  <si>
+    <t>MA5300</t>
+  </si>
+  <si>
+    <t>Mars high tonnage</t>
+  </si>
+  <si>
+    <t>JU Series</t>
+  </si>
+  <si>
+    <t>JU1200</t>
+  </si>
+  <si>
+    <t>Servo hydraulic</t>
+  </si>
+  <si>
+    <t>JU1600</t>
+  </si>
+  <si>
+    <t>Servo mid-size</t>
+  </si>
+  <si>
+    <t>JU2000</t>
+  </si>
+  <si>
+    <t>Servo mid-high</t>
+  </si>
+  <si>
+    <t>JU2500</t>
+  </si>
+  <si>
+    <t>Servo large</t>
+  </si>
+  <si>
+    <t>JU3200</t>
+  </si>
+  <si>
+    <t>Servo larger</t>
+  </si>
+  <si>
+    <t>JU3800</t>
+  </si>
+  <si>
+    <t>Servo heavy</t>
+  </si>
+  <si>
+    <t>Zhafir VE</t>
+  </si>
+  <si>
+    <t>VE1200</t>
+  </si>
+  <si>
+    <t>Electric precision</t>
+  </si>
+  <si>
+    <t>VE1600</t>
+  </si>
+  <si>
+    <t>Electric mid-size</t>
+  </si>
+  <si>
+    <t>VE2000</t>
+  </si>
+  <si>
+    <t>Electric standard</t>
+  </si>
+  <si>
+    <t>VE2300</t>
+  </si>
+  <si>
+    <t>Electric extended</t>
+  </si>
+  <si>
+    <t>VE2800</t>
+  </si>
+  <si>
+    <t>Electric larger</t>
+  </si>
+  <si>
+    <t>VE3200</t>
+  </si>
+  <si>
+    <t>Electric high force</t>
+  </si>
+  <si>
+    <t>VE3600</t>
+  </si>
+  <si>
+    <t>Electric heavy</t>
+  </si>
+  <si>
+    <t>VE4500</t>
+  </si>
+  <si>
+    <t>Electric large</t>
+  </si>
+  <si>
+    <t>Zhafir ZE</t>
+  </si>
+  <si>
+    <t>ZE120</t>
+  </si>
+  <si>
+    <t>ZE300</t>
+  </si>
+  <si>
+    <t>Compact electric</t>
+  </si>
+  <si>
+    <t>ZE600</t>
+  </si>
+  <si>
+    <t>Mid electric</t>
+  </si>
+  <si>
+    <t>ZE900</t>
+  </si>
+  <si>
+    <t>ZE1400</t>
+  </si>
+  <si>
+    <t>ZE1800</t>
+  </si>
+  <si>
+    <t>Electric mid-high</t>
+  </si>
+  <si>
     <t>NETSTAL</t>
   </si>
   <si>
@@ -86,6 +674,114 @@
   </si>
   <si>
     <t>ELION 800</t>
+  </si>
+  <si>
+    <t>ELION 1000</t>
+  </si>
+  <si>
+    <t>Mid precision</t>
+  </si>
+  <si>
+    <t>ELION 1200</t>
+  </si>
+  <si>
+    <t>ELION 1750</t>
+  </si>
+  <si>
+    <t>ELION 2200</t>
+  </si>
+  <si>
+    <t>ELION 2800</t>
+  </si>
+  <si>
+    <t>ELION 3200</t>
+  </si>
+  <si>
+    <t>ELION 4200</t>
+  </si>
+  <si>
+    <t>ELION 5000</t>
+  </si>
+  <si>
+    <t>EVOS</t>
+  </si>
+  <si>
+    <t>EVOS 1200</t>
+  </si>
+  <si>
+    <t>Hybrid machine</t>
+  </si>
+  <si>
+    <t>EVOS 1750</t>
+  </si>
+  <si>
+    <t>Hybrid mid</t>
+  </si>
+  <si>
+    <t>EVOS 2200</t>
+  </si>
+  <si>
+    <t>Hybrid standard</t>
+  </si>
+  <si>
+    <t>EVOS 2800</t>
+  </si>
+  <si>
+    <t>Hybrid large</t>
+  </si>
+  <si>
+    <t>EVOS 3200</t>
+  </si>
+  <si>
+    <t>Hybrid high force</t>
+  </si>
+  <si>
+    <t>EVOS 4200</t>
+  </si>
+  <si>
+    <t>EVOS 5000</t>
+  </si>
+  <si>
+    <t>PET-LINE</t>
+  </si>
+  <si>
+    <t>PET 2000</t>
+  </si>
+  <si>
+    <t>PET preform high speed</t>
+  </si>
+  <si>
+    <t>PET 3000</t>
+  </si>
+  <si>
+    <t>PET medium</t>
+  </si>
+  <si>
+    <t>PET 4000</t>
+  </si>
+  <si>
+    <t>PET large</t>
+  </si>
+  <si>
+    <t>PET 5000</t>
+  </si>
+  <si>
+    <t>PET heavy</t>
+  </si>
+  <si>
+    <t>SYNCHRO</t>
+  </si>
+  <si>
+    <t>SYNCHRO 2200</t>
+  </si>
+  <si>
+    <t>SYNCHRO 3200</t>
+  </si>
+  <si>
+    <t>SYNCHRO 4200</t>
+  </si>
+  <si>
+    <t>High-speed heavy</t>
   </si>
 </sst>
 </file>
@@ -448,7 +1144,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -510,7 +1207,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -521,120 +1218,4800 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>55</v>
+        <v>1100</v>
       </c>
       <c r="E2">
-        <v>520</v>
+        <v>2000</v>
       </c>
       <c r="F2">
-        <v>480</v>
+        <v>1830</v>
       </c>
       <c r="G2">
-        <v>320</v>
+        <v>1400</v>
       </c>
       <c r="H2">
-        <v>320</v>
+        <v>1150</v>
       </c>
       <c r="I2">
-        <v>550</v>
+        <v>2400</v>
       </c>
       <c r="J2">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="K2">
-        <v>350</v>
+        <v>1200</v>
       </c>
       <c r="L2">
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="M2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E3">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="F3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G3">
-        <v>340</v>
+        <v>650</v>
       </c>
       <c r="H3">
-        <v>340</v>
+        <v>600</v>
       </c>
       <c r="I3">
+        <v>800</v>
+      </c>
+      <c r="J3">
+        <v>150</v>
+      </c>
+      <c r="K3">
         <v>600</v>
       </c>
-      <c r="J3">
-        <v>160</v>
-      </c>
-      <c r="K3">
-        <v>380</v>
-      </c>
       <c r="L3">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="M3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4">
+        <v>500</v>
+      </c>
+      <c r="E4">
+        <v>1200</v>
+      </c>
+      <c r="F4">
+        <v>1200</v>
+      </c>
+      <c r="G4">
+        <v>840</v>
+      </c>
+      <c r="H4">
+        <v>840</v>
+      </c>
+      <c r="I4">
+        <v>1560</v>
+      </c>
+      <c r="J4">
+        <v>300</v>
+      </c>
+      <c r="K4">
+        <v>860</v>
+      </c>
+      <c r="L4">
+        <v>700</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>650</v>
+      </c>
+      <c r="F5">
+        <v>430</v>
+      </c>
+      <c r="G5">
+        <v>650</v>
+      </c>
+      <c r="H5">
+        <v>430</v>
+      </c>
+      <c r="I5">
+        <v>520</v>
+      </c>
+      <c r="J5">
+        <v>190</v>
+      </c>
+      <c r="K5">
+        <v>520</v>
+      </c>
+      <c r="L5">
+        <v>330</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6">
+        <v>380</v>
+      </c>
+      <c r="E6">
+        <v>1050</v>
+      </c>
+      <c r="F6">
+        <v>950</v>
+      </c>
+      <c r="G6">
+        <v>1050</v>
+      </c>
+      <c r="H6">
+        <v>950</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>450</v>
+      </c>
+      <c r="F7">
+        <v>450</v>
+      </c>
+      <c r="G7">
+        <v>270</v>
+      </c>
+      <c r="H7">
+        <v>270</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7">
+        <v>150</v>
+      </c>
+      <c r="K7">
+        <v>300</v>
+      </c>
+      <c r="L7">
+        <v>300</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>500</v>
+      </c>
+      <c r="F8">
+        <v>500</v>
+      </c>
+      <c r="G8">
+        <v>320</v>
+      </c>
+      <c r="H8">
+        <v>320</v>
+      </c>
+      <c r="I8">
+        <v>550</v>
+      </c>
+      <c r="J8">
+        <v>150</v>
+      </c>
+      <c r="K8">
+        <v>350</v>
+      </c>
+      <c r="L8">
+        <v>320</v>
+      </c>
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>570</v>
+      </c>
+      <c r="F9">
+        <v>570</v>
+      </c>
+      <c r="G9">
+        <v>320</v>
+      </c>
+      <c r="H9">
+        <v>320</v>
+      </c>
+      <c r="I9">
+        <v>600</v>
+      </c>
+      <c r="J9">
+        <v>200</v>
+      </c>
+      <c r="K9">
+        <v>400</v>
+      </c>
+      <c r="L9">
+        <v>400</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
+        <v>150</v>
+      </c>
+      <c r="E10">
+        <v>570</v>
+      </c>
+      <c r="F10">
+        <v>570</v>
+      </c>
+      <c r="G10">
+        <v>320</v>
+      </c>
+      <c r="H10">
+        <v>320</v>
+      </c>
+      <c r="I10">
+        <v>600</v>
+      </c>
+      <c r="J10">
+        <v>200</v>
+      </c>
+      <c r="K10">
+        <v>450</v>
+      </c>
+      <c r="L10">
+        <v>450</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>290</v>
+      </c>
+      <c r="E11">
+        <v>770</v>
+      </c>
+      <c r="F11">
+        <v>770</v>
+      </c>
+      <c r="G11">
+        <v>470</v>
+      </c>
+      <c r="H11">
+        <v>470</v>
+      </c>
+      <c r="I11">
+        <v>800</v>
+      </c>
+      <c r="J11">
+        <v>250</v>
+      </c>
+      <c r="K11">
+        <v>600</v>
+      </c>
+      <c r="L11">
+        <v>600</v>
+      </c>
+      <c r="M11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12">
+        <v>150</v>
+      </c>
+      <c r="E12">
+        <v>770</v>
+      </c>
+      <c r="F12">
+        <v>770</v>
+      </c>
+      <c r="G12">
+        <v>470</v>
+      </c>
+      <c r="H12">
+        <v>470</v>
+      </c>
+      <c r="I12">
+        <v>900</v>
+      </c>
+      <c r="J12">
+        <v>250</v>
+      </c>
+      <c r="K12">
+        <v>650</v>
+      </c>
+      <c r="L12">
+        <v>650</v>
+      </c>
+      <c r="M12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13">
+        <v>350</v>
+      </c>
+      <c r="E13">
+        <v>850</v>
+      </c>
+      <c r="F13">
+        <v>850</v>
+      </c>
+      <c r="G13">
+        <v>550</v>
+      </c>
+      <c r="H13">
+        <v>550</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13">
+        <v>300</v>
+      </c>
+      <c r="K13">
+        <v>700</v>
+      </c>
+      <c r="L13">
+        <v>700</v>
+      </c>
+      <c r="M13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14">
+        <v>400</v>
+      </c>
+      <c r="E14">
+        <v>900</v>
+      </c>
+      <c r="F14">
+        <v>900</v>
+      </c>
+      <c r="G14">
+        <v>600</v>
+      </c>
+      <c r="H14">
+        <v>600</v>
+      </c>
+      <c r="I14">
+        <v>1100</v>
+      </c>
+      <c r="J14">
+        <v>300</v>
+      </c>
+      <c r="K14">
+        <v>800</v>
+      </c>
+      <c r="L14">
+        <v>800</v>
+      </c>
+      <c r="M14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15">
+        <v>800</v>
+      </c>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15">
+        <v>1000</v>
+      </c>
+      <c r="G15">
+        <v>700</v>
+      </c>
+      <c r="H15">
+        <v>700</v>
+      </c>
+      <c r="I15">
+        <v>1300</v>
+      </c>
+      <c r="J15">
+        <v>350</v>
+      </c>
+      <c r="K15">
+        <v>900</v>
+      </c>
+      <c r="L15">
+        <v>900</v>
+      </c>
+      <c r="M15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16">
+        <v>800</v>
+      </c>
+      <c r="E16">
+        <v>1100</v>
+      </c>
+      <c r="F16">
+        <v>1100</v>
+      </c>
+      <c r="G16">
+        <v>800</v>
+      </c>
+      <c r="H16">
+        <v>800</v>
+      </c>
+      <c r="I16">
+        <v>1400</v>
+      </c>
+      <c r="J16">
+        <v>400</v>
+      </c>
+      <c r="K16">
+        <v>1000</v>
+      </c>
+      <c r="L16">
+        <v>1000</v>
+      </c>
+      <c r="M16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17">
+        <v>1300</v>
+      </c>
+      <c r="E17">
+        <v>1300</v>
+      </c>
+      <c r="F17">
+        <v>1300</v>
+      </c>
+      <c r="G17">
+        <v>900</v>
+      </c>
+      <c r="H17">
+        <v>900</v>
+      </c>
+      <c r="I17">
+        <v>1800</v>
+      </c>
+      <c r="J17">
+        <v>500</v>
+      </c>
+      <c r="K17">
+        <v>1200</v>
+      </c>
+      <c r="L17">
+        <v>1200</v>
+      </c>
+      <c r="M17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18">
+        <v>2100</v>
+      </c>
+      <c r="E18">
+        <v>1500</v>
+      </c>
+      <c r="F18">
+        <v>1500</v>
+      </c>
+      <c r="G18">
+        <v>1100</v>
+      </c>
+      <c r="H18">
+        <v>1100</v>
+      </c>
+      <c r="I18">
+        <v>2000</v>
+      </c>
+      <c r="J18">
+        <v>600</v>
+      </c>
+      <c r="K18">
+        <v>1400</v>
+      </c>
+      <c r="L18">
+        <v>1400</v>
+      </c>
+      <c r="M18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
+        <v>500</v>
+      </c>
+      <c r="F19">
+        <v>500</v>
+      </c>
+      <c r="G19">
+        <v>320</v>
+      </c>
+      <c r="H19">
+        <v>320</v>
+      </c>
+      <c r="I19">
+        <v>550</v>
+      </c>
+      <c r="J19">
+        <v>150</v>
+      </c>
+      <c r="K19">
+        <v>350</v>
+      </c>
+      <c r="L19">
+        <v>320</v>
+      </c>
+      <c r="M19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20">
+        <v>150</v>
+      </c>
+      <c r="E20">
+        <v>570</v>
+      </c>
+      <c r="F20">
+        <v>570</v>
+      </c>
+      <c r="G20">
+        <v>320</v>
+      </c>
+      <c r="H20">
+        <v>320</v>
+      </c>
+      <c r="I20">
+        <v>600</v>
+      </c>
+      <c r="J20">
+        <v>200</v>
+      </c>
+      <c r="K20">
+        <v>450</v>
+      </c>
+      <c r="L20">
+        <v>400</v>
+      </c>
+      <c r="M20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21">
+        <v>290</v>
+      </c>
+      <c r="E21">
+        <v>770</v>
+      </c>
+      <c r="F21">
+        <v>770</v>
+      </c>
+      <c r="G21">
+        <v>470</v>
+      </c>
+      <c r="H21">
+        <v>470</v>
+      </c>
+      <c r="I21">
+        <v>800</v>
+      </c>
+      <c r="J21">
+        <v>250</v>
+      </c>
+      <c r="K21">
+        <v>600</v>
+      </c>
+      <c r="L21">
+        <v>600</v>
+      </c>
+      <c r="M21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22">
+        <v>150</v>
+      </c>
+      <c r="E22">
+        <v>770</v>
+      </c>
+      <c r="F22">
+        <v>770</v>
+      </c>
+      <c r="G22">
+        <v>470</v>
+      </c>
+      <c r="H22">
+        <v>470</v>
+      </c>
+      <c r="I22">
+        <v>900</v>
+      </c>
+      <c r="J22">
+        <v>250</v>
+      </c>
+      <c r="K22">
+        <v>650</v>
+      </c>
+      <c r="L22">
+        <v>650</v>
+      </c>
+      <c r="M22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23">
+        <v>350</v>
+      </c>
+      <c r="E23">
+        <v>850</v>
+      </c>
+      <c r="F23">
+        <v>850</v>
+      </c>
+      <c r="G23">
+        <v>550</v>
+      </c>
+      <c r="H23">
+        <v>550</v>
+      </c>
+      <c r="I23">
+        <v>1000</v>
+      </c>
+      <c r="J23">
+        <v>300</v>
+      </c>
+      <c r="K23">
+        <v>700</v>
+      </c>
+      <c r="L23">
+        <v>700</v>
+      </c>
+      <c r="M23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24">
+        <v>400</v>
+      </c>
+      <c r="E24">
+        <v>900</v>
+      </c>
+      <c r="F24">
+        <v>900</v>
+      </c>
+      <c r="G24">
+        <v>600</v>
+      </c>
+      <c r="H24">
+        <v>600</v>
+      </c>
+      <c r="I24">
+        <v>1100</v>
+      </c>
+      <c r="J24">
+        <v>300</v>
+      </c>
+      <c r="K24">
+        <v>800</v>
+      </c>
+      <c r="L24">
+        <v>800</v>
+      </c>
+      <c r="M24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25">
+        <v>800</v>
+      </c>
+      <c r="E25">
+        <v>1000</v>
+      </c>
+      <c r="F25">
+        <v>1000</v>
+      </c>
+      <c r="G25">
+        <v>700</v>
+      </c>
+      <c r="H25">
+        <v>700</v>
+      </c>
+      <c r="I25">
+        <v>1300</v>
+      </c>
+      <c r="J25">
+        <v>350</v>
+      </c>
+      <c r="K25">
+        <v>900</v>
+      </c>
+      <c r="L25">
+        <v>900</v>
+      </c>
+      <c r="M25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26">
+        <v>800</v>
+      </c>
+      <c r="E26">
+        <v>1100</v>
+      </c>
+      <c r="F26">
+        <v>1100</v>
+      </c>
+      <c r="G26">
+        <v>800</v>
+      </c>
+      <c r="H26">
+        <v>800</v>
+      </c>
+      <c r="I26">
+        <v>1400</v>
+      </c>
+      <c r="J26">
+        <v>400</v>
+      </c>
+      <c r="K26">
+        <v>1000</v>
+      </c>
+      <c r="L26">
+        <v>1000</v>
+      </c>
+      <c r="M26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27">
+        <v>1300</v>
+      </c>
+      <c r="E27">
+        <v>1300</v>
+      </c>
+      <c r="F27">
+        <v>1300</v>
+      </c>
+      <c r="G27">
+        <v>900</v>
+      </c>
+      <c r="H27">
+        <v>900</v>
+      </c>
+      <c r="I27">
+        <v>1800</v>
+      </c>
+      <c r="J27">
+        <v>500</v>
+      </c>
+      <c r="K27">
+        <v>1200</v>
+      </c>
+      <c r="L27">
+        <v>1200</v>
+      </c>
+      <c r="M27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28">
+        <v>290</v>
+      </c>
+      <c r="E28">
+        <v>770</v>
+      </c>
+      <c r="F28">
+        <v>770</v>
+      </c>
+      <c r="G28">
+        <v>470</v>
+      </c>
+      <c r="H28">
+        <v>470</v>
+      </c>
+      <c r="I28">
+        <v>800</v>
+      </c>
+      <c r="J28">
+        <v>250</v>
+      </c>
+      <c r="K28">
+        <v>600</v>
+      </c>
+      <c r="L28">
+        <v>600</v>
+      </c>
+      <c r="M28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29">
+        <v>350</v>
+      </c>
+      <c r="E29">
+        <v>850</v>
+      </c>
+      <c r="F29">
+        <v>850</v>
+      </c>
+      <c r="G29">
+        <v>550</v>
+      </c>
+      <c r="H29">
+        <v>550</v>
+      </c>
+      <c r="I29">
+        <v>1000</v>
+      </c>
+      <c r="J29">
+        <v>300</v>
+      </c>
+      <c r="K29">
+        <v>700</v>
+      </c>
+      <c r="L29">
+        <v>700</v>
+      </c>
+      <c r="M29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30">
+        <v>400</v>
+      </c>
+      <c r="E30">
+        <v>900</v>
+      </c>
+      <c r="F30">
+        <v>900</v>
+      </c>
+      <c r="G30">
+        <v>600</v>
+      </c>
+      <c r="H30">
+        <v>600</v>
+      </c>
+      <c r="I30">
+        <v>1100</v>
+      </c>
+      <c r="J30">
+        <v>300</v>
+      </c>
+      <c r="K30">
+        <v>800</v>
+      </c>
+      <c r="L30">
+        <v>800</v>
+      </c>
+      <c r="M30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31">
+        <v>800</v>
+      </c>
+      <c r="E31">
+        <v>1000</v>
+      </c>
+      <c r="F31">
+        <v>1000</v>
+      </c>
+      <c r="G31">
+        <v>700</v>
+      </c>
+      <c r="H31">
+        <v>700</v>
+      </c>
+      <c r="I31">
+        <v>1300</v>
+      </c>
+      <c r="J31">
+        <v>350</v>
+      </c>
+      <c r="K31">
+        <v>900</v>
+      </c>
+      <c r="L31">
+        <v>900</v>
+      </c>
+      <c r="M31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32">
+        <v>800</v>
+      </c>
+      <c r="E32">
+        <v>1100</v>
+      </c>
+      <c r="F32">
+        <v>1100</v>
+      </c>
+      <c r="G32">
+        <v>800</v>
+      </c>
+      <c r="H32">
+        <v>800</v>
+      </c>
+      <c r="I32">
+        <v>1400</v>
+      </c>
+      <c r="J32">
+        <v>400</v>
+      </c>
+      <c r="K32">
+        <v>1000</v>
+      </c>
+      <c r="L32">
+        <v>1000</v>
+      </c>
+      <c r="M32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
         <v>85</v>
       </c>
-      <c r="E4">
+      <c r="D33">
+        <v>1300</v>
+      </c>
+      <c r="E33">
+        <v>1300</v>
+      </c>
+      <c r="F33">
+        <v>1300</v>
+      </c>
+      <c r="G33">
+        <v>900</v>
+      </c>
+      <c r="H33">
+        <v>900</v>
+      </c>
+      <c r="I33">
+        <v>1800</v>
+      </c>
+      <c r="J33">
+        <v>500</v>
+      </c>
+      <c r="K33">
+        <v>1200</v>
+      </c>
+      <c r="L33">
+        <v>1200</v>
+      </c>
+      <c r="M33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34">
+        <v>2100</v>
+      </c>
+      <c r="E34">
+        <v>1500</v>
+      </c>
+      <c r="F34">
+        <v>1500</v>
+      </c>
+      <c r="G34">
+        <v>1100</v>
+      </c>
+      <c r="H34">
+        <v>1100</v>
+      </c>
+      <c r="I34">
+        <v>2000</v>
+      </c>
+      <c r="J34">
+        <v>600</v>
+      </c>
+      <c r="K34">
+        <v>1400</v>
+      </c>
+      <c r="L34">
+        <v>1400</v>
+      </c>
+      <c r="M34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>30</v>
+      </c>
+      <c r="E35">
+        <v>350</v>
+      </c>
+      <c r="F35">
+        <v>350</v>
+      </c>
+      <c r="G35">
+        <v>350</v>
+      </c>
+      <c r="H35">
+        <v>350</v>
+      </c>
+      <c r="I35">
+        <v>400</v>
+      </c>
+      <c r="J35">
+        <v>120</v>
+      </c>
+      <c r="K35">
+        <v>250</v>
+      </c>
+      <c r="L35">
+        <v>200</v>
+      </c>
+      <c r="M35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36">
+        <v>60</v>
+      </c>
+      <c r="E36">
+        <v>450</v>
+      </c>
+      <c r="F36">
+        <v>450</v>
+      </c>
+      <c r="G36">
+        <v>450</v>
+      </c>
+      <c r="H36">
+        <v>450</v>
+      </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36">
+        <v>150</v>
+      </c>
+      <c r="K36">
+        <v>300</v>
+      </c>
+      <c r="L36">
+        <v>300</v>
+      </c>
+      <c r="M36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37">
+        <v>100</v>
+      </c>
+      <c r="E37">
+        <v>500</v>
+      </c>
+      <c r="F37">
+        <v>500</v>
+      </c>
+      <c r="G37">
+        <v>500</v>
+      </c>
+      <c r="H37">
+        <v>500</v>
+      </c>
+      <c r="I37">
+        <v>500</v>
+      </c>
+      <c r="J37">
+        <v>150</v>
+      </c>
+      <c r="K37">
+        <v>350</v>
+      </c>
+      <c r="L37">
+        <v>300</v>
+      </c>
+      <c r="M37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38">
+        <v>55</v>
+      </c>
+      <c r="E38">
+        <v>560</v>
+      </c>
+      <c r="F38">
+        <v>510</v>
+      </c>
+      <c r="G38">
+        <v>360</v>
+      </c>
+      <c r="H38">
+        <v>360</v>
+      </c>
+      <c r="I38">
+        <v>600</v>
+      </c>
+      <c r="J38">
+        <v>200</v>
+      </c>
+      <c r="K38">
+        <v>400</v>
+      </c>
+      <c r="L38">
+        <v>350</v>
+      </c>
+      <c r="M38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>75</v>
+      </c>
+      <c r="E39">
+        <v>630</v>
+      </c>
+      <c r="F39">
+        <v>580</v>
+      </c>
+      <c r="G39">
+        <v>410</v>
+      </c>
+      <c r="H39">
+        <v>410</v>
+      </c>
+      <c r="I39">
+        <v>700</v>
+      </c>
+      <c r="J39">
+        <v>200</v>
+      </c>
+      <c r="K39">
+        <v>450</v>
+      </c>
+      <c r="L39">
+        <v>400</v>
+      </c>
+      <c r="M39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40">
+        <v>143</v>
+      </c>
+      <c r="E40">
+        <v>750</v>
+      </c>
+      <c r="F40">
+        <v>680</v>
+      </c>
+      <c r="G40">
+        <v>510</v>
+      </c>
+      <c r="H40">
+        <v>510</v>
+      </c>
+      <c r="I40">
+        <v>800</v>
+      </c>
+      <c r="J40">
+        <v>250</v>
+      </c>
+      <c r="K40">
+        <v>550</v>
+      </c>
+      <c r="L40">
+        <v>500</v>
+      </c>
+      <c r="M40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41">
+        <v>198</v>
+      </c>
+      <c r="E41">
+        <v>830</v>
+      </c>
+      <c r="F41">
+        <v>760</v>
+      </c>
+      <c r="G41">
+        <v>560</v>
+      </c>
+      <c r="H41">
+        <v>560</v>
+      </c>
+      <c r="I41">
+        <v>900</v>
+      </c>
+      <c r="J41">
+        <v>300</v>
+      </c>
+      <c r="K41">
+        <v>600</v>
+      </c>
+      <c r="L41">
+        <v>600</v>
+      </c>
+      <c r="M41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42">
+        <v>308</v>
+      </c>
+      <c r="E42">
+        <v>900</v>
+      </c>
+      <c r="F42">
+        <v>840</v>
+      </c>
+      <c r="G42">
+        <v>610</v>
+      </c>
+      <c r="H42">
+        <v>610</v>
+      </c>
+      <c r="I42">
+        <v>1000</v>
+      </c>
+      <c r="J42">
+        <v>300</v>
+      </c>
+      <c r="K42">
+        <v>700</v>
+      </c>
+      <c r="L42">
+        <v>700</v>
+      </c>
+      <c r="M42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43">
+        <v>385</v>
+      </c>
+      <c r="E43">
+        <v>1020</v>
+      </c>
+      <c r="F43">
+        <v>950</v>
+      </c>
+      <c r="G43">
+        <v>710</v>
+      </c>
+      <c r="H43">
+        <v>710</v>
+      </c>
+      <c r="I43">
+        <v>1200</v>
+      </c>
+      <c r="J43">
+        <v>350</v>
+      </c>
+      <c r="K43">
+        <v>800</v>
+      </c>
+      <c r="L43">
+        <v>800</v>
+      </c>
+      <c r="M43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44">
+        <v>495</v>
+      </c>
+      <c r="E44">
+        <v>1150</v>
+      </c>
+      <c r="F44">
+        <v>1050</v>
+      </c>
+      <c r="G44">
+        <v>820</v>
+      </c>
+      <c r="H44">
+        <v>820</v>
+      </c>
+      <c r="I44">
+        <v>1300</v>
+      </c>
+      <c r="J44">
+        <v>400</v>
+      </c>
+      <c r="K44">
+        <v>900</v>
+      </c>
+      <c r="L44">
+        <v>900</v>
+      </c>
+      <c r="M44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45">
+        <v>550</v>
+      </c>
+      <c r="E45">
+        <v>1250</v>
+      </c>
+      <c r="F45">
+        <v>1150</v>
+      </c>
+      <c r="G45">
+        <v>920</v>
+      </c>
+      <c r="H45">
+        <v>920</v>
+      </c>
+      <c r="I45">
+        <v>1400</v>
+      </c>
+      <c r="J45">
+        <v>450</v>
+      </c>
+      <c r="K45">
+        <v>1000</v>
+      </c>
+      <c r="L45">
+        <v>1000</v>
+      </c>
+      <c r="M45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46">
+        <v>143</v>
+      </c>
+      <c r="E46">
+        <v>750</v>
+      </c>
+      <c r="F46">
+        <v>680</v>
+      </c>
+      <c r="G46">
+        <v>510</v>
+      </c>
+      <c r="H46">
+        <v>510</v>
+      </c>
+      <c r="I46">
+        <v>800</v>
+      </c>
+      <c r="J46">
+        <v>250</v>
+      </c>
+      <c r="K46">
+        <v>550</v>
+      </c>
+      <c r="L46">
+        <v>500</v>
+      </c>
+      <c r="M46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47">
+        <v>198</v>
+      </c>
+      <c r="E47">
+        <v>830</v>
+      </c>
+      <c r="F47">
+        <v>760</v>
+      </c>
+      <c r="G47">
+        <v>560</v>
+      </c>
+      <c r="H47">
+        <v>560</v>
+      </c>
+      <c r="I47">
+        <v>900</v>
+      </c>
+      <c r="J47">
+        <v>300</v>
+      </c>
+      <c r="K47">
+        <v>600</v>
+      </c>
+      <c r="L47">
+        <v>600</v>
+      </c>
+      <c r="M47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48">
+        <v>242</v>
+      </c>
+      <c r="E48">
+        <v>880</v>
+      </c>
+      <c r="F48">
+        <v>810</v>
+      </c>
+      <c r="G48">
+        <v>610</v>
+      </c>
+      <c r="H48">
+        <v>610</v>
+      </c>
+      <c r="I48">
+        <v>1000</v>
+      </c>
+      <c r="J48">
+        <v>300</v>
+      </c>
+      <c r="K48">
+        <v>700</v>
+      </c>
+      <c r="L48">
+        <v>700</v>
+      </c>
+      <c r="M48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49">
+        <v>308</v>
+      </c>
+      <c r="E49">
+        <v>950</v>
+      </c>
+      <c r="F49">
+        <v>850</v>
+      </c>
+      <c r="G49">
+        <v>660</v>
+      </c>
+      <c r="H49">
+        <v>660</v>
+      </c>
+      <c r="I49">
+        <v>1100</v>
+      </c>
+      <c r="J49">
+        <v>350</v>
+      </c>
+      <c r="K49">
+        <v>750</v>
+      </c>
+      <c r="L49">
+        <v>750</v>
+      </c>
+      <c r="M49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50">
+        <v>385</v>
+      </c>
+      <c r="E50">
+        <v>1050</v>
+      </c>
+      <c r="F50">
+        <v>950</v>
+      </c>
+      <c r="G50">
+        <v>710</v>
+      </c>
+      <c r="H50">
+        <v>710</v>
+      </c>
+      <c r="I50">
+        <v>1200</v>
+      </c>
+      <c r="J50">
+        <v>400</v>
+      </c>
+      <c r="K50">
+        <v>800</v>
+      </c>
+      <c r="L50">
+        <v>800</v>
+      </c>
+      <c r="M50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51">
+        <v>33</v>
+      </c>
+      <c r="E51">
+        <v>450</v>
+      </c>
+      <c r="F51">
+        <v>420</v>
+      </c>
+      <c r="G51">
+        <v>300</v>
+      </c>
+      <c r="H51">
+        <v>300</v>
+      </c>
+      <c r="I51">
+        <v>500</v>
+      </c>
+      <c r="J51">
+        <v>150</v>
+      </c>
+      <c r="K51">
+        <v>300</v>
+      </c>
+      <c r="L51">
+        <v>300</v>
+      </c>
+      <c r="M51" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52">
+        <v>55</v>
+      </c>
+      <c r="E52">
+        <v>560</v>
+      </c>
+      <c r="F52">
+        <v>510</v>
+      </c>
+      <c r="G52">
+        <v>360</v>
+      </c>
+      <c r="H52">
+        <v>360</v>
+      </c>
+      <c r="I52">
+        <v>600</v>
+      </c>
+      <c r="J52">
+        <v>200</v>
+      </c>
+      <c r="K52">
+        <v>400</v>
+      </c>
+      <c r="L52">
+        <v>350</v>
+      </c>
+      <c r="M52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53">
+        <v>75</v>
+      </c>
+      <c r="E53">
+        <v>630</v>
+      </c>
+      <c r="F53">
+        <v>580</v>
+      </c>
+      <c r="G53">
+        <v>410</v>
+      </c>
+      <c r="H53">
+        <v>410</v>
+      </c>
+      <c r="I53">
+        <v>700</v>
+      </c>
+      <c r="J53">
+        <v>200</v>
+      </c>
+      <c r="K53">
+        <v>450</v>
+      </c>
+      <c r="L53">
+        <v>400</v>
+      </c>
+      <c r="M53" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54">
+        <v>143</v>
+      </c>
+      <c r="E54">
+        <v>750</v>
+      </c>
+      <c r="F54">
+        <v>680</v>
+      </c>
+      <c r="G54">
+        <v>510</v>
+      </c>
+      <c r="H54">
+        <v>510</v>
+      </c>
+      <c r="I54">
+        <v>800</v>
+      </c>
+      <c r="J54">
+        <v>250</v>
+      </c>
+      <c r="K54">
+        <v>550</v>
+      </c>
+      <c r="L54">
+        <v>500</v>
+      </c>
+      <c r="M54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55">
+        <v>198</v>
+      </c>
+      <c r="E55">
+        <v>830</v>
+      </c>
+      <c r="F55">
+        <v>760</v>
+      </c>
+      <c r="G55">
+        <v>560</v>
+      </c>
+      <c r="H55">
+        <v>560</v>
+      </c>
+      <c r="I55">
+        <v>900</v>
+      </c>
+      <c r="J55">
+        <v>300</v>
+      </c>
+      <c r="K55">
+        <v>600</v>
+      </c>
+      <c r="L55">
+        <v>600</v>
+      </c>
+      <c r="M55" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" t="s">
+        <v>133</v>
+      </c>
+      <c r="D56">
+        <v>308</v>
+      </c>
+      <c r="E56">
+        <v>900</v>
+      </c>
+      <c r="F56">
+        <v>840</v>
+      </c>
+      <c r="G56">
+        <v>610</v>
+      </c>
+      <c r="H56">
+        <v>610</v>
+      </c>
+      <c r="I56">
+        <v>1000</v>
+      </c>
+      <c r="J56">
+        <v>300</v>
+      </c>
+      <c r="K56">
+        <v>700</v>
+      </c>
+      <c r="L56">
+        <v>700</v>
+      </c>
+      <c r="M56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57">
+        <v>385</v>
+      </c>
+      <c r="E57">
+        <v>1020</v>
+      </c>
+      <c r="F57">
+        <v>950</v>
+      </c>
+      <c r="G57">
+        <v>710</v>
+      </c>
+      <c r="H57">
+        <v>710</v>
+      </c>
+      <c r="I57">
+        <v>1200</v>
+      </c>
+      <c r="J57">
+        <v>350</v>
+      </c>
+      <c r="K57">
+        <v>800</v>
+      </c>
+      <c r="L57">
+        <v>800</v>
+      </c>
+      <c r="M57" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58">
+        <v>220</v>
+      </c>
+      <c r="E58">
+        <v>880</v>
+      </c>
+      <c r="F58">
+        <v>810</v>
+      </c>
+      <c r="G58">
+        <v>610</v>
+      </c>
+      <c r="H58">
+        <v>610</v>
+      </c>
+      <c r="I58">
+        <v>1000</v>
+      </c>
+      <c r="J58">
+        <v>300</v>
+      </c>
+      <c r="K58">
+        <v>700</v>
+      </c>
+      <c r="L58">
+        <v>700</v>
+      </c>
+      <c r="M58" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59">
+        <v>350</v>
+      </c>
+      <c r="E59">
+        <v>1050</v>
+      </c>
+      <c r="F59">
+        <v>950</v>
+      </c>
+      <c r="G59">
+        <v>710</v>
+      </c>
+      <c r="H59">
+        <v>710</v>
+      </c>
+      <c r="I59">
+        <v>1200</v>
+      </c>
+      <c r="J59">
+        <v>400</v>
+      </c>
+      <c r="K59">
+        <v>800</v>
+      </c>
+      <c r="L59">
+        <v>800</v>
+      </c>
+      <c r="M59" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>96</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" t="s">
+        <v>141</v>
+      </c>
+      <c r="D60">
+        <v>450</v>
+      </c>
+      <c r="E60">
+        <v>1150</v>
+      </c>
+      <c r="F60">
+        <v>1050</v>
+      </c>
+      <c r="G60">
+        <v>820</v>
+      </c>
+      <c r="H60">
+        <v>820</v>
+      </c>
+      <c r="I60">
+        <v>1300</v>
+      </c>
+      <c r="J60">
+        <v>400</v>
+      </c>
+      <c r="K60">
+        <v>900</v>
+      </c>
+      <c r="L60">
+        <v>900</v>
+      </c>
+      <c r="M60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61">
+        <v>500</v>
+      </c>
+      <c r="E61">
+        <v>1250</v>
+      </c>
+      <c r="F61">
+        <v>1150</v>
+      </c>
+      <c r="G61">
+        <v>920</v>
+      </c>
+      <c r="H61">
+        <v>920</v>
+      </c>
+      <c r="I61">
+        <v>1400</v>
+      </c>
+      <c r="J61">
+        <v>450</v>
+      </c>
+      <c r="K61">
+        <v>1000</v>
+      </c>
+      <c r="L61">
+        <v>1000</v>
+      </c>
+      <c r="M61" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62">
+        <v>231</v>
+      </c>
+      <c r="E62">
+        <v>880</v>
+      </c>
+      <c r="F62">
+        <v>810</v>
+      </c>
+      <c r="G62">
+        <v>610</v>
+      </c>
+      <c r="H62">
+        <v>610</v>
+      </c>
+      <c r="I62">
+        <v>1000</v>
+      </c>
+      <c r="J62">
+        <v>300</v>
+      </c>
+      <c r="K62">
+        <v>700</v>
+      </c>
+      <c r="L62">
+        <v>700</v>
+      </c>
+      <c r="M62" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63">
+        <v>308</v>
+      </c>
+      <c r="E63">
+        <v>950</v>
+      </c>
+      <c r="F63">
+        <v>850</v>
+      </c>
+      <c r="G63">
+        <v>660</v>
+      </c>
+      <c r="H63">
+        <v>660</v>
+      </c>
+      <c r="I63">
+        <v>1100</v>
+      </c>
+      <c r="J63">
+        <v>350</v>
+      </c>
+      <c r="K63">
+        <v>750</v>
+      </c>
+      <c r="L63">
+        <v>750</v>
+      </c>
+      <c r="M63" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>96</v>
+      </c>
+      <c r="B64" t="s">
+        <v>145</v>
+      </c>
+      <c r="C64" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64">
+        <v>385</v>
+      </c>
+      <c r="E64">
+        <v>1050</v>
+      </c>
+      <c r="F64">
+        <v>950</v>
+      </c>
+      <c r="G64">
+        <v>710</v>
+      </c>
+      <c r="H64">
+        <v>710</v>
+      </c>
+      <c r="I64">
+        <v>1200</v>
+      </c>
+      <c r="J64">
+        <v>400</v>
+      </c>
+      <c r="K64">
+        <v>800</v>
+      </c>
+      <c r="L64">
+        <v>800</v>
+      </c>
+      <c r="M64" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" t="s">
+        <v>151</v>
+      </c>
+      <c r="D65">
+        <v>550</v>
+      </c>
+      <c r="E65">
+        <v>1250</v>
+      </c>
+      <c r="F65">
+        <v>1150</v>
+      </c>
+      <c r="G65">
+        <v>920</v>
+      </c>
+      <c r="H65">
+        <v>920</v>
+      </c>
+      <c r="I65">
+        <v>1400</v>
+      </c>
+      <c r="J65">
+        <v>450</v>
+      </c>
+      <c r="K65">
+        <v>1000</v>
+      </c>
+      <c r="L65">
+        <v>1000</v>
+      </c>
+      <c r="M65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66">
+        <v>130</v>
+      </c>
+      <c r="E66">
+        <v>750</v>
+      </c>
+      <c r="F66">
+        <v>700</v>
+      </c>
+      <c r="G66">
+        <v>500</v>
+      </c>
+      <c r="H66">
+        <v>500</v>
+      </c>
+      <c r="I66">
+        <v>800</v>
+      </c>
+      <c r="J66">
+        <v>250</v>
+      </c>
+      <c r="K66">
+        <v>550</v>
+      </c>
+      <c r="L66">
+        <v>500</v>
+      </c>
+      <c r="M66" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" t="s">
+        <v>154</v>
+      </c>
+      <c r="C67" t="s">
+        <v>157</v>
+      </c>
+      <c r="D67">
+        <v>180</v>
+      </c>
+      <c r="E67">
+        <v>850</v>
+      </c>
+      <c r="F67">
+        <v>800</v>
+      </c>
+      <c r="G67">
+        <v>580</v>
+      </c>
+      <c r="H67">
+        <v>580</v>
+      </c>
+      <c r="I67">
+        <v>900</v>
+      </c>
+      <c r="J67">
+        <v>300</v>
+      </c>
+      <c r="K67">
+        <v>600</v>
+      </c>
+      <c r="L67">
+        <v>600</v>
+      </c>
+      <c r="M67" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68">
+        <v>220</v>
+      </c>
+      <c r="E68">
+        <v>900</v>
+      </c>
+      <c r="F68">
+        <v>850</v>
+      </c>
+      <c r="G68">
+        <v>610</v>
+      </c>
+      <c r="H68">
+        <v>610</v>
+      </c>
+      <c r="I68">
+        <v>1000</v>
+      </c>
+      <c r="J68">
+        <v>300</v>
+      </c>
+      <c r="K68">
+        <v>700</v>
+      </c>
+      <c r="L68">
         <v>650</v>
       </c>
-      <c r="F4">
+      <c r="M68" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" t="s">
+        <v>161</v>
+      </c>
+      <c r="D69">
+        <v>280</v>
+      </c>
+      <c r="E69">
+        <v>950</v>
+      </c>
+      <c r="F69">
+        <v>900</v>
+      </c>
+      <c r="G69">
+        <v>660</v>
+      </c>
+      <c r="H69">
+        <v>660</v>
+      </c>
+      <c r="I69">
+        <v>1100</v>
+      </c>
+      <c r="J69">
+        <v>350</v>
+      </c>
+      <c r="K69">
+        <v>750</v>
+      </c>
+      <c r="L69">
+        <v>700</v>
+      </c>
+      <c r="M69" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" t="s">
+        <v>163</v>
+      </c>
+      <c r="D70">
+        <v>350</v>
+      </c>
+      <c r="E70">
+        <v>1050</v>
+      </c>
+      <c r="F70">
+        <v>950</v>
+      </c>
+      <c r="G70">
+        <v>710</v>
+      </c>
+      <c r="H70">
+        <v>710</v>
+      </c>
+      <c r="I70">
+        <v>1200</v>
+      </c>
+      <c r="J70">
+        <v>400</v>
+      </c>
+      <c r="K70">
+        <v>800</v>
+      </c>
+      <c r="L70">
+        <v>800</v>
+      </c>
+      <c r="M70" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71">
+        <v>420</v>
+      </c>
+      <c r="E71">
+        <v>1150</v>
+      </c>
+      <c r="F71">
+        <v>1050</v>
+      </c>
+      <c r="G71">
+        <v>820</v>
+      </c>
+      <c r="H71">
+        <v>820</v>
+      </c>
+      <c r="I71">
+        <v>1300</v>
+      </c>
+      <c r="J71">
+        <v>400</v>
+      </c>
+      <c r="K71">
+        <v>900</v>
+      </c>
+      <c r="L71">
+        <v>900</v>
+      </c>
+      <c r="M71" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72">
+        <v>520</v>
+      </c>
+      <c r="E72">
+        <v>1250</v>
+      </c>
+      <c r="F72">
+        <v>1150</v>
+      </c>
+      <c r="G72">
+        <v>920</v>
+      </c>
+      <c r="H72">
+        <v>920</v>
+      </c>
+      <c r="I72">
+        <v>1400</v>
+      </c>
+      <c r="J72">
+        <v>450</v>
+      </c>
+      <c r="K72">
+        <v>1000</v>
+      </c>
+      <c r="L72">
+        <v>1000</v>
+      </c>
+      <c r="M72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>168</v>
+      </c>
+      <c r="D73">
+        <v>600</v>
+      </c>
+      <c r="E73">
+        <v>1350</v>
+      </c>
+      <c r="F73">
+        <v>1250</v>
+      </c>
+      <c r="G73">
+        <v>1020</v>
+      </c>
+      <c r="H73">
+        <v>1020</v>
+      </c>
+      <c r="I73">
+        <v>1500</v>
+      </c>
+      <c r="J73">
+        <v>500</v>
+      </c>
+      <c r="K73">
+        <v>1100</v>
+      </c>
+      <c r="L73">
+        <v>1100</v>
+      </c>
+      <c r="M73" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" t="s">
+        <v>171</v>
+      </c>
+      <c r="D74">
+        <v>130</v>
+      </c>
+      <c r="E74">
+        <v>750</v>
+      </c>
+      <c r="F74">
+        <v>700</v>
+      </c>
+      <c r="G74">
+        <v>500</v>
+      </c>
+      <c r="H74">
+        <v>500</v>
+      </c>
+      <c r="I74">
+        <v>800</v>
+      </c>
+      <c r="J74">
+        <v>250</v>
+      </c>
+      <c r="K74">
+        <v>550</v>
+      </c>
+      <c r="L74">
+        <v>500</v>
+      </c>
+      <c r="M74" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75">
+        <v>180</v>
+      </c>
+      <c r="E75">
+        <v>850</v>
+      </c>
+      <c r="F75">
+        <v>800</v>
+      </c>
+      <c r="G75">
+        <v>580</v>
+      </c>
+      <c r="H75">
+        <v>580</v>
+      </c>
+      <c r="I75">
+        <v>900</v>
+      </c>
+      <c r="J75">
+        <v>300</v>
+      </c>
+      <c r="K75">
+        <v>600</v>
+      </c>
+      <c r="L75">
+        <v>600</v>
+      </c>
+      <c r="M75" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" t="s">
+        <v>175</v>
+      </c>
+      <c r="D76">
+        <v>220</v>
+      </c>
+      <c r="E76">
+        <v>900</v>
+      </c>
+      <c r="F76">
+        <v>850</v>
+      </c>
+      <c r="G76">
+        <v>610</v>
+      </c>
+      <c r="H76">
+        <v>610</v>
+      </c>
+      <c r="I76">
+        <v>1000</v>
+      </c>
+      <c r="J76">
+        <v>300</v>
+      </c>
+      <c r="K76">
+        <v>700</v>
+      </c>
+      <c r="L76">
+        <v>650</v>
+      </c>
+      <c r="M76" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77">
+        <v>280</v>
+      </c>
+      <c r="E77">
+        <v>950</v>
+      </c>
+      <c r="F77">
+        <v>900</v>
+      </c>
+      <c r="G77">
+        <v>660</v>
+      </c>
+      <c r="H77">
+        <v>660</v>
+      </c>
+      <c r="I77">
+        <v>1100</v>
+      </c>
+      <c r="J77">
+        <v>350</v>
+      </c>
+      <c r="K77">
+        <v>750</v>
+      </c>
+      <c r="L77">
+        <v>700</v>
+      </c>
+      <c r="M77" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78">
+        <v>350</v>
+      </c>
+      <c r="E78">
+        <v>1050</v>
+      </c>
+      <c r="F78">
+        <v>950</v>
+      </c>
+      <c r="G78">
+        <v>710</v>
+      </c>
+      <c r="H78">
+        <v>710</v>
+      </c>
+      <c r="I78">
+        <v>1200</v>
+      </c>
+      <c r="J78">
+        <v>400</v>
+      </c>
+      <c r="K78">
+        <v>800</v>
+      </c>
+      <c r="L78">
+        <v>800</v>
+      </c>
+      <c r="M78" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" t="s">
+        <v>170</v>
+      </c>
+      <c r="C79" t="s">
+        <v>181</v>
+      </c>
+      <c r="D79">
+        <v>420</v>
+      </c>
+      <c r="E79">
+        <v>1150</v>
+      </c>
+      <c r="F79">
+        <v>1050</v>
+      </c>
+      <c r="G79">
+        <v>820</v>
+      </c>
+      <c r="H79">
+        <v>820</v>
+      </c>
+      <c r="I79">
+        <v>1300</v>
+      </c>
+      <c r="J79">
+        <v>400</v>
+      </c>
+      <c r="K79">
+        <v>900</v>
+      </c>
+      <c r="L79">
+        <v>900</v>
+      </c>
+      <c r="M79" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80">
+        <v>130</v>
+      </c>
+      <c r="E80">
+        <v>750</v>
+      </c>
+      <c r="F80">
+        <v>700</v>
+      </c>
+      <c r="G80">
+        <v>500</v>
+      </c>
+      <c r="H80">
+        <v>500</v>
+      </c>
+      <c r="I80">
+        <v>800</v>
+      </c>
+      <c r="J80">
+        <v>250</v>
+      </c>
+      <c r="K80">
+        <v>550</v>
+      </c>
+      <c r="L80">
+        <v>500</v>
+      </c>
+      <c r="M80" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" t="s">
+        <v>186</v>
+      </c>
+      <c r="D81">
+        <v>180</v>
+      </c>
+      <c r="E81">
+        <v>850</v>
+      </c>
+      <c r="F81">
+        <v>800</v>
+      </c>
+      <c r="G81">
+        <v>580</v>
+      </c>
+      <c r="H81">
+        <v>580</v>
+      </c>
+      <c r="I81">
+        <v>900</v>
+      </c>
+      <c r="J81">
+        <v>300</v>
+      </c>
+      <c r="K81">
+        <v>600</v>
+      </c>
+      <c r="L81">
+        <v>600</v>
+      </c>
+      <c r="M81" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" t="s">
+        <v>188</v>
+      </c>
+      <c r="D82">
+        <v>220</v>
+      </c>
+      <c r="E82">
+        <v>900</v>
+      </c>
+      <c r="F82">
+        <v>850</v>
+      </c>
+      <c r="G82">
+        <v>610</v>
+      </c>
+      <c r="H82">
+        <v>610</v>
+      </c>
+      <c r="I82">
+        <v>1000</v>
+      </c>
+      <c r="J82">
+        <v>300</v>
+      </c>
+      <c r="K82">
+        <v>700</v>
+      </c>
+      <c r="L82">
+        <v>650</v>
+      </c>
+      <c r="M82" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>153</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" t="s">
+        <v>190</v>
+      </c>
+      <c r="D83">
+        <v>250</v>
+      </c>
+      <c r="E83">
+        <v>930</v>
+      </c>
+      <c r="F83">
+        <v>880</v>
+      </c>
+      <c r="G83">
+        <v>640</v>
+      </c>
+      <c r="H83">
+        <v>640</v>
+      </c>
+      <c r="I83">
+        <v>1050</v>
+      </c>
+      <c r="J83">
+        <v>320</v>
+      </c>
+      <c r="K83">
+        <v>720</v>
+      </c>
+      <c r="L83">
+        <v>680</v>
+      </c>
+      <c r="M83" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>153</v>
+      </c>
+      <c r="B84" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" t="s">
+        <v>192</v>
+      </c>
+      <c r="D84">
+        <v>300</v>
+      </c>
+      <c r="E84">
+        <v>980</v>
+      </c>
+      <c r="F84">
+        <v>930</v>
+      </c>
+      <c r="G84">
+        <v>680</v>
+      </c>
+      <c r="H84">
+        <v>680</v>
+      </c>
+      <c r="I84">
+        <v>1100</v>
+      </c>
+      <c r="J84">
+        <v>350</v>
+      </c>
+      <c r="K84">
+        <v>760</v>
+      </c>
+      <c r="L84">
+        <v>700</v>
+      </c>
+      <c r="M84" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>153</v>
+      </c>
+      <c r="B85" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" t="s">
+        <v>194</v>
+      </c>
+      <c r="D85">
+        <v>350</v>
+      </c>
+      <c r="E85">
+        <v>1050</v>
+      </c>
+      <c r="F85">
+        <v>950</v>
+      </c>
+      <c r="G85">
+        <v>710</v>
+      </c>
+      <c r="H85">
+        <v>710</v>
+      </c>
+      <c r="I85">
+        <v>1200</v>
+      </c>
+      <c r="J85">
+        <v>400</v>
+      </c>
+      <c r="K85">
+        <v>800</v>
+      </c>
+      <c r="L85">
+        <v>800</v>
+      </c>
+      <c r="M85" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86">
+        <v>400</v>
+      </c>
+      <c r="E86">
+        <v>1100</v>
+      </c>
+      <c r="F86">
+        <v>1000</v>
+      </c>
+      <c r="G86">
+        <v>750</v>
+      </c>
+      <c r="H86">
+        <v>750</v>
+      </c>
+      <c r="I86">
+        <v>1250</v>
+      </c>
+      <c r="J86">
+        <v>420</v>
+      </c>
+      <c r="K86">
+        <v>850</v>
+      </c>
+      <c r="L86">
+        <v>850</v>
+      </c>
+      <c r="M86" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>153</v>
+      </c>
+      <c r="B87" t="s">
+        <v>183</v>
+      </c>
+      <c r="C87" t="s">
+        <v>198</v>
+      </c>
+      <c r="D87">
+        <v>500</v>
+      </c>
+      <c r="E87">
+        <v>1200</v>
+      </c>
+      <c r="F87">
+        <v>1100</v>
+      </c>
+      <c r="G87">
+        <v>820</v>
+      </c>
+      <c r="H87">
+        <v>820</v>
+      </c>
+      <c r="I87">
+        <v>1350</v>
+      </c>
+      <c r="J87">
+        <v>450</v>
+      </c>
+      <c r="K87">
+        <v>950</v>
+      </c>
+      <c r="L87">
+        <v>900</v>
+      </c>
+      <c r="M87" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" t="s">
+        <v>200</v>
+      </c>
+      <c r="C88" t="s">
+        <v>201</v>
+      </c>
+      <c r="D88">
+        <v>13</v>
+      </c>
+      <c r="E88">
+        <v>350</v>
+      </c>
+      <c r="F88">
+        <v>300</v>
+      </c>
+      <c r="G88">
+        <v>200</v>
+      </c>
+      <c r="H88">
+        <v>200</v>
+      </c>
+      <c r="I88">
+        <v>400</v>
+      </c>
+      <c r="J88">
+        <v>120</v>
+      </c>
+      <c r="K88">
+        <v>250</v>
+      </c>
+      <c r="L88">
+        <v>200</v>
+      </c>
+      <c r="M88" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>153</v>
+      </c>
+      <c r="B89" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" t="s">
+        <v>202</v>
+      </c>
+      <c r="D89">
+        <v>33</v>
+      </c>
+      <c r="E89">
+        <v>450</v>
+      </c>
+      <c r="F89">
+        <v>420</v>
+      </c>
+      <c r="G89">
+        <v>280</v>
+      </c>
+      <c r="H89">
+        <v>280</v>
+      </c>
+      <c r="I89">
+        <v>500</v>
+      </c>
+      <c r="J89">
+        <v>150</v>
+      </c>
+      <c r="K89">
+        <v>300</v>
+      </c>
+      <c r="L89">
+        <v>300</v>
+      </c>
+      <c r="M89" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>153</v>
+      </c>
+      <c r="B90" t="s">
+        <v>200</v>
+      </c>
+      <c r="C90" t="s">
+        <v>204</v>
+      </c>
+      <c r="D90">
+        <v>66</v>
+      </c>
+      <c r="E90">
+        <v>550</v>
+      </c>
+      <c r="F90">
+        <v>500</v>
+      </c>
+      <c r="G90">
+        <v>350</v>
+      </c>
+      <c r="H90">
+        <v>350</v>
+      </c>
+      <c r="I90">
+        <v>600</v>
+      </c>
+      <c r="J90">
+        <v>200</v>
+      </c>
+      <c r="K90">
+        <v>400</v>
+      </c>
+      <c r="L90">
+        <v>350</v>
+      </c>
+      <c r="M90" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>153</v>
+      </c>
+      <c r="B91" t="s">
+        <v>200</v>
+      </c>
+      <c r="C91" t="s">
+        <v>206</v>
+      </c>
+      <c r="D91">
+        <v>100</v>
+      </c>
+      <c r="E91">
+        <v>650</v>
+      </c>
+      <c r="F91">
+        <v>600</v>
+      </c>
+      <c r="G91">
+        <v>420</v>
+      </c>
+      <c r="H91">
+        <v>420</v>
+      </c>
+      <c r="I91">
+        <v>700</v>
+      </c>
+      <c r="J91">
+        <v>200</v>
+      </c>
+      <c r="K91">
+        <v>450</v>
+      </c>
+      <c r="L91">
+        <v>400</v>
+      </c>
+      <c r="M91" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" t="s">
+        <v>200</v>
+      </c>
+      <c r="C92" t="s">
+        <v>207</v>
+      </c>
+      <c r="D92">
+        <v>150</v>
+      </c>
+      <c r="E92">
+        <v>750</v>
+      </c>
+      <c r="F92">
+        <v>680</v>
+      </c>
+      <c r="G92">
+        <v>500</v>
+      </c>
+      <c r="H92">
+        <v>500</v>
+      </c>
+      <c r="I92">
+        <v>800</v>
+      </c>
+      <c r="J92">
+        <v>250</v>
+      </c>
+      <c r="K92">
+        <v>550</v>
+      </c>
+      <c r="L92">
+        <v>500</v>
+      </c>
+      <c r="M92" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>153</v>
+      </c>
+      <c r="B93" t="s">
+        <v>200</v>
+      </c>
+      <c r="C93" t="s">
+        <v>208</v>
+      </c>
+      <c r="D93">
+        <v>200</v>
+      </c>
+      <c r="E93">
+        <v>830</v>
+      </c>
+      <c r="F93">
+        <v>760</v>
+      </c>
+      <c r="G93">
+        <v>560</v>
+      </c>
+      <c r="H93">
+        <v>560</v>
+      </c>
+      <c r="I93">
+        <v>900</v>
+      </c>
+      <c r="J93">
+        <v>300</v>
+      </c>
+      <c r="K93">
+        <v>600</v>
+      </c>
+      <c r="L93">
+        <v>600</v>
+      </c>
+      <c r="M93" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>210</v>
+      </c>
+      <c r="B94" t="s">
+        <v>211</v>
+      </c>
+      <c r="C94" t="s">
+        <v>212</v>
+      </c>
+      <c r="D94">
+        <v>55</v>
+      </c>
+      <c r="E94">
+        <v>520</v>
+      </c>
+      <c r="F94">
+        <v>480</v>
+      </c>
+      <c r="G94">
+        <v>320</v>
+      </c>
+      <c r="H94">
+        <v>320</v>
+      </c>
+      <c r="I94">
+        <v>550</v>
+      </c>
+      <c r="J94">
+        <v>150</v>
+      </c>
+      <c r="K94">
+        <v>350</v>
+      </c>
+      <c r="L94">
+        <v>300</v>
+      </c>
+      <c r="M94" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" t="s">
+        <v>214</v>
+      </c>
+      <c r="D95">
+        <v>65</v>
+      </c>
+      <c r="E95">
+        <v>550</v>
+      </c>
+      <c r="F95">
+        <v>500</v>
+      </c>
+      <c r="G95">
+        <v>340</v>
+      </c>
+      <c r="H95">
+        <v>340</v>
+      </c>
+      <c r="I95">
+        <v>600</v>
+      </c>
+      <c r="J95">
+        <v>160</v>
+      </c>
+      <c r="K95">
+        <v>380</v>
+      </c>
+      <c r="L95">
+        <v>320</v>
+      </c>
+      <c r="M95" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" t="s">
+        <v>216</v>
+      </c>
+      <c r="D96">
+        <v>85</v>
+      </c>
+      <c r="E96">
+        <v>650</v>
+      </c>
+      <c r="F96">
         <v>621</v>
       </c>
-      <c r="G4">
+      <c r="G96">
         <v>410</v>
       </c>
-      <c r="H4">
+      <c r="H96">
         <v>410</v>
       </c>
-      <c r="I4">
+      <c r="I96">
         <v>650</v>
       </c>
-      <c r="J4">
+      <c r="J96">
         <v>180</v>
       </c>
-      <c r="K4">
+      <c r="K96">
         <v>450</v>
       </c>
-      <c r="L4">
+      <c r="L96">
         <v>400</v>
       </c>
-      <c r="M4" t="s">
-        <v>17</v>
+      <c r="M96" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>210</v>
+      </c>
+      <c r="B97" t="s">
+        <v>211</v>
+      </c>
+      <c r="C97" t="s">
+        <v>217</v>
+      </c>
+      <c r="D97">
+        <v>110</v>
+      </c>
+      <c r="E97">
+        <v>680</v>
+      </c>
+      <c r="F97">
+        <v>620</v>
+      </c>
+      <c r="G97">
+        <v>450</v>
+      </c>
+      <c r="H97">
+        <v>450</v>
+      </c>
+      <c r="I97">
+        <v>750</v>
+      </c>
+      <c r="J97">
+        <v>220</v>
+      </c>
+      <c r="K97">
+        <v>500</v>
+      </c>
+      <c r="L97">
+        <v>450</v>
+      </c>
+      <c r="M97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>210</v>
+      </c>
+      <c r="B98" t="s">
+        <v>211</v>
+      </c>
+      <c r="C98" t="s">
+        <v>219</v>
+      </c>
+      <c r="D98">
+        <v>130</v>
+      </c>
+      <c r="E98">
+        <v>750</v>
+      </c>
+      <c r="F98">
+        <v>700</v>
+      </c>
+      <c r="G98">
+        <v>500</v>
+      </c>
+      <c r="H98">
+        <v>500</v>
+      </c>
+      <c r="I98">
+        <v>800</v>
+      </c>
+      <c r="J98">
+        <v>250</v>
+      </c>
+      <c r="K98">
+        <v>550</v>
+      </c>
+      <c r="L98">
+        <v>500</v>
+      </c>
+      <c r="M98" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" t="s">
+        <v>211</v>
+      </c>
+      <c r="C99" t="s">
+        <v>220</v>
+      </c>
+      <c r="D99">
+        <v>190</v>
+      </c>
+      <c r="E99">
+        <v>820</v>
+      </c>
+      <c r="F99">
+        <v>760</v>
+      </c>
+      <c r="G99">
+        <v>560</v>
+      </c>
+      <c r="H99">
+        <v>560</v>
+      </c>
+      <c r="I99">
+        <v>900</v>
+      </c>
+      <c r="J99">
+        <v>300</v>
+      </c>
+      <c r="K99">
+        <v>600</v>
+      </c>
+      <c r="L99">
+        <v>600</v>
+      </c>
+      <c r="M99" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>210</v>
+      </c>
+      <c r="B100" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" t="s">
+        <v>221</v>
+      </c>
+      <c r="D100">
+        <v>240</v>
+      </c>
+      <c r="E100">
+        <v>900</v>
+      </c>
+      <c r="F100">
+        <v>830</v>
+      </c>
+      <c r="G100">
+        <v>610</v>
+      </c>
+      <c r="H100">
+        <v>610</v>
+      </c>
+      <c r="I100">
+        <v>1000</v>
+      </c>
+      <c r="J100">
+        <v>300</v>
+      </c>
+      <c r="K100">
+        <v>700</v>
+      </c>
+      <c r="L100">
+        <v>700</v>
+      </c>
+      <c r="M100" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" t="s">
+        <v>211</v>
+      </c>
+      <c r="C101" t="s">
+        <v>222</v>
+      </c>
+      <c r="D101">
+        <v>310</v>
+      </c>
+      <c r="E101">
+        <v>950</v>
+      </c>
+      <c r="F101">
+        <v>880</v>
+      </c>
+      <c r="G101">
+        <v>660</v>
+      </c>
+      <c r="H101">
+        <v>660</v>
+      </c>
+      <c r="I101">
+        <v>1100</v>
+      </c>
+      <c r="J101">
+        <v>350</v>
+      </c>
+      <c r="K101">
+        <v>750</v>
+      </c>
+      <c r="L101">
+        <v>750</v>
+      </c>
+      <c r="M101" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>210</v>
+      </c>
+      <c r="B102" t="s">
+        <v>211</v>
+      </c>
+      <c r="C102" t="s">
+        <v>223</v>
+      </c>
+      <c r="D102">
+        <v>350</v>
+      </c>
+      <c r="E102">
+        <v>1050</v>
+      </c>
+      <c r="F102">
+        <v>950</v>
+      </c>
+      <c r="G102">
+        <v>710</v>
+      </c>
+      <c r="H102">
+        <v>710</v>
+      </c>
+      <c r="I102">
+        <v>1200</v>
+      </c>
+      <c r="J102">
+        <v>400</v>
+      </c>
+      <c r="K102">
+        <v>800</v>
+      </c>
+      <c r="L102">
+        <v>800</v>
+      </c>
+      <c r="M102" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>210</v>
+      </c>
+      <c r="B103" t="s">
+        <v>211</v>
+      </c>
+      <c r="C103" t="s">
+        <v>224</v>
+      </c>
+      <c r="D103">
+        <v>460</v>
+      </c>
+      <c r="E103">
+        <v>1150</v>
+      </c>
+      <c r="F103">
+        <v>1050</v>
+      </c>
+      <c r="G103">
+        <v>820</v>
+      </c>
+      <c r="H103">
+        <v>820</v>
+      </c>
+      <c r="I103">
+        <v>1300</v>
+      </c>
+      <c r="J103">
+        <v>400</v>
+      </c>
+      <c r="K103">
+        <v>900</v>
+      </c>
+      <c r="L103">
+        <v>900</v>
+      </c>
+      <c r="M103" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>210</v>
+      </c>
+      <c r="B104" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" t="s">
+        <v>225</v>
+      </c>
+      <c r="D104">
+        <v>550</v>
+      </c>
+      <c r="E104">
+        <v>1250</v>
+      </c>
+      <c r="F104">
+        <v>1150</v>
+      </c>
+      <c r="G104">
+        <v>920</v>
+      </c>
+      <c r="H104">
+        <v>920</v>
+      </c>
+      <c r="I104">
+        <v>1400</v>
+      </c>
+      <c r="J104">
+        <v>450</v>
+      </c>
+      <c r="K104">
+        <v>1000</v>
+      </c>
+      <c r="L104">
+        <v>1000</v>
+      </c>
+      <c r="M104" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" t="s">
+        <v>226</v>
+      </c>
+      <c r="C105" t="s">
+        <v>227</v>
+      </c>
+      <c r="D105">
+        <v>130</v>
+      </c>
+      <c r="E105">
+        <v>750</v>
+      </c>
+      <c r="F105">
+        <v>700</v>
+      </c>
+      <c r="G105">
+        <v>500</v>
+      </c>
+      <c r="H105">
+        <v>500</v>
+      </c>
+      <c r="I105">
+        <v>800</v>
+      </c>
+      <c r="J105">
+        <v>250</v>
+      </c>
+      <c r="K105">
+        <v>550</v>
+      </c>
+      <c r="L105">
+        <v>500</v>
+      </c>
+      <c r="M105" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
+        <v>226</v>
+      </c>
+      <c r="C106" t="s">
+        <v>229</v>
+      </c>
+      <c r="D106">
+        <v>190</v>
+      </c>
+      <c r="E106">
+        <v>820</v>
+      </c>
+      <c r="F106">
+        <v>760</v>
+      </c>
+      <c r="G106">
+        <v>560</v>
+      </c>
+      <c r="H106">
+        <v>560</v>
+      </c>
+      <c r="I106">
+        <v>900</v>
+      </c>
+      <c r="J106">
+        <v>300</v>
+      </c>
+      <c r="K106">
+        <v>600</v>
+      </c>
+      <c r="L106">
+        <v>600</v>
+      </c>
+      <c r="M106" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" t="s">
+        <v>226</v>
+      </c>
+      <c r="C107" t="s">
+        <v>231</v>
+      </c>
+      <c r="D107">
+        <v>240</v>
+      </c>
+      <c r="E107">
+        <v>900</v>
+      </c>
+      <c r="F107">
+        <v>830</v>
+      </c>
+      <c r="G107">
+        <v>610</v>
+      </c>
+      <c r="H107">
+        <v>610</v>
+      </c>
+      <c r="I107">
+        <v>1000</v>
+      </c>
+      <c r="J107">
+        <v>300</v>
+      </c>
+      <c r="K107">
+        <v>700</v>
+      </c>
+      <c r="L107">
+        <v>700</v>
+      </c>
+      <c r="M107" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>210</v>
+      </c>
+      <c r="B108" t="s">
+        <v>226</v>
+      </c>
+      <c r="C108" t="s">
+        <v>233</v>
+      </c>
+      <c r="D108">
+        <v>310</v>
+      </c>
+      <c r="E108">
+        <v>950</v>
+      </c>
+      <c r="F108">
+        <v>880</v>
+      </c>
+      <c r="G108">
+        <v>660</v>
+      </c>
+      <c r="H108">
+        <v>660</v>
+      </c>
+      <c r="I108">
+        <v>1100</v>
+      </c>
+      <c r="J108">
+        <v>350</v>
+      </c>
+      <c r="K108">
+        <v>750</v>
+      </c>
+      <c r="L108">
+        <v>750</v>
+      </c>
+      <c r="M108" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>210</v>
+      </c>
+      <c r="B109" t="s">
+        <v>226</v>
+      </c>
+      <c r="C109" t="s">
+        <v>235</v>
+      </c>
+      <c r="D109">
+        <v>350</v>
+      </c>
+      <c r="E109">
+        <v>1050</v>
+      </c>
+      <c r="F109">
+        <v>950</v>
+      </c>
+      <c r="G109">
+        <v>710</v>
+      </c>
+      <c r="H109">
+        <v>710</v>
+      </c>
+      <c r="I109">
+        <v>1200</v>
+      </c>
+      <c r="J109">
+        <v>400</v>
+      </c>
+      <c r="K109">
+        <v>800</v>
+      </c>
+      <c r="L109">
+        <v>800</v>
+      </c>
+      <c r="M109" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>210</v>
+      </c>
+      <c r="B110" t="s">
+        <v>226</v>
+      </c>
+      <c r="C110" t="s">
+        <v>237</v>
+      </c>
+      <c r="D110">
+        <v>460</v>
+      </c>
+      <c r="E110">
+        <v>1150</v>
+      </c>
+      <c r="F110">
+        <v>1050</v>
+      </c>
+      <c r="G110">
+        <v>820</v>
+      </c>
+      <c r="H110">
+        <v>820</v>
+      </c>
+      <c r="I110">
+        <v>1300</v>
+      </c>
+      <c r="J110">
+        <v>400</v>
+      </c>
+      <c r="K110">
+        <v>900</v>
+      </c>
+      <c r="L110">
+        <v>900</v>
+      </c>
+      <c r="M110" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>210</v>
+      </c>
+      <c r="B111" t="s">
+        <v>226</v>
+      </c>
+      <c r="C111" t="s">
+        <v>238</v>
+      </c>
+      <c r="D111">
+        <v>550</v>
+      </c>
+      <c r="E111">
+        <v>1250</v>
+      </c>
+      <c r="F111">
+        <v>1150</v>
+      </c>
+      <c r="G111">
+        <v>920</v>
+      </c>
+      <c r="H111">
+        <v>920</v>
+      </c>
+      <c r="I111">
+        <v>1400</v>
+      </c>
+      <c r="J111">
+        <v>450</v>
+      </c>
+      <c r="K111">
+        <v>1000</v>
+      </c>
+      <c r="L111">
+        <v>1000</v>
+      </c>
+      <c r="M111" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>210</v>
+      </c>
+      <c r="B112" t="s">
+        <v>239</v>
+      </c>
+      <c r="C112" t="s">
+        <v>240</v>
+      </c>
+      <c r="D112">
+        <v>220</v>
+      </c>
+      <c r="E112">
+        <v>880</v>
+      </c>
+      <c r="F112">
+        <v>810</v>
+      </c>
+      <c r="G112">
+        <v>610</v>
+      </c>
+      <c r="H112">
+        <v>610</v>
+      </c>
+      <c r="I112">
+        <v>1000</v>
+      </c>
+      <c r="J112">
+        <v>300</v>
+      </c>
+      <c r="K112">
+        <v>700</v>
+      </c>
+      <c r="L112">
+        <v>700</v>
+      </c>
+      <c r="M112" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>210</v>
+      </c>
+      <c r="B113" t="s">
+        <v>239</v>
+      </c>
+      <c r="C113" t="s">
+        <v>242</v>
+      </c>
+      <c r="D113">
+        <v>350</v>
+      </c>
+      <c r="E113">
+        <v>1050</v>
+      </c>
+      <c r="F113">
+        <v>950</v>
+      </c>
+      <c r="G113">
+        <v>710</v>
+      </c>
+      <c r="H113">
+        <v>710</v>
+      </c>
+      <c r="I113">
+        <v>1200</v>
+      </c>
+      <c r="J113">
+        <v>400</v>
+      </c>
+      <c r="K113">
+        <v>800</v>
+      </c>
+      <c r="L113">
+        <v>800</v>
+      </c>
+      <c r="M113" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>210</v>
+      </c>
+      <c r="B114" t="s">
+        <v>239</v>
+      </c>
+      <c r="C114" t="s">
+        <v>244</v>
+      </c>
+      <c r="D114">
+        <v>450</v>
+      </c>
+      <c r="E114">
+        <v>1150</v>
+      </c>
+      <c r="F114">
+        <v>1050</v>
+      </c>
+      <c r="G114">
+        <v>820</v>
+      </c>
+      <c r="H114">
+        <v>820</v>
+      </c>
+      <c r="I114">
+        <v>1300</v>
+      </c>
+      <c r="J114">
+        <v>400</v>
+      </c>
+      <c r="K114">
+        <v>900</v>
+      </c>
+      <c r="L114">
+        <v>900</v>
+      </c>
+      <c r="M114" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>210</v>
+      </c>
+      <c r="B115" t="s">
+        <v>239</v>
+      </c>
+      <c r="C115" t="s">
+        <v>246</v>
+      </c>
+      <c r="D115">
+        <v>550</v>
+      </c>
+      <c r="E115">
+        <v>1250</v>
+      </c>
+      <c r="F115">
+        <v>1150</v>
+      </c>
+      <c r="G115">
+        <v>920</v>
+      </c>
+      <c r="H115">
+        <v>920</v>
+      </c>
+      <c r="I115">
+        <v>1400</v>
+      </c>
+      <c r="J115">
+        <v>450</v>
+      </c>
+      <c r="K115">
+        <v>1000</v>
+      </c>
+      <c r="L115">
+        <v>1000</v>
+      </c>
+      <c r="M115" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>210</v>
+      </c>
+      <c r="B116" t="s">
+        <v>248</v>
+      </c>
+      <c r="C116" t="s">
+        <v>249</v>
+      </c>
+      <c r="D116">
+        <v>240</v>
+      </c>
+      <c r="E116">
+        <v>900</v>
+      </c>
+      <c r="F116">
+        <v>830</v>
+      </c>
+      <c r="G116">
+        <v>610</v>
+      </c>
+      <c r="H116">
+        <v>610</v>
+      </c>
+      <c r="I116">
+        <v>1000</v>
+      </c>
+      <c r="J116">
+        <v>300</v>
+      </c>
+      <c r="K116">
+        <v>700</v>
+      </c>
+      <c r="L116">
+        <v>700</v>
+      </c>
+      <c r="M116" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>210</v>
+      </c>
+      <c r="B117" t="s">
+        <v>248</v>
+      </c>
+      <c r="C117" t="s">
+        <v>250</v>
+      </c>
+      <c r="D117">
+        <v>350</v>
+      </c>
+      <c r="E117">
+        <v>1050</v>
+      </c>
+      <c r="F117">
+        <v>950</v>
+      </c>
+      <c r="G117">
+        <v>710</v>
+      </c>
+      <c r="H117">
+        <v>710</v>
+      </c>
+      <c r="I117">
+        <v>1200</v>
+      </c>
+      <c r="J117">
+        <v>400</v>
+      </c>
+      <c r="K117">
+        <v>800</v>
+      </c>
+      <c r="L117">
+        <v>800</v>
+      </c>
+      <c r="M117" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>210</v>
+      </c>
+      <c r="B118" t="s">
+        <v>248</v>
+      </c>
+      <c r="C118" t="s">
+        <v>251</v>
+      </c>
+      <c r="D118">
+        <v>460</v>
+      </c>
+      <c r="E118">
+        <v>1150</v>
+      </c>
+      <c r="F118">
+        <v>1050</v>
+      </c>
+      <c r="G118">
+        <v>820</v>
+      </c>
+      <c r="H118">
+        <v>820</v>
+      </c>
+      <c r="I118">
+        <v>1300</v>
+      </c>
+      <c r="J118">
+        <v>400</v>
+      </c>
+      <c r="K118">
+        <v>900</v>
+      </c>
+      <c r="L118">
+        <v>900</v>
+      </c>
+      <c r="M118" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N26" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N118" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ELION"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
